--- a/mode_docx_gen/pmi_ka2/ka_modes/КА_10.xlsx
+++ b/mode_docx_gen/pmi_ka2/ka_modes/КА_10.xlsx
@@ -1122,8 +1122,8 @@
       <c r="G2" t="n">
         <v>0</v>
       </c>
-      <c r="H2" s="2" t="n">
-        <v>1</v>
+      <c r="H2" t="n">
+        <v>0</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -1209,8 +1209,8 @@
       <c r="AJ2" t="n">
         <v>0</v>
       </c>
-      <c r="AK2" t="n">
-        <v>0</v>
+      <c r="AK2" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -1517,9 +1517,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1652,9 +1652,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="AH2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -1682,9 +1682,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="AN2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
